--- a/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>单据编号</t>
   </si>
@@ -49,9 +49,6 @@
     <t>下单类型</t>
   </si>
   <si>
-    <t>关联任务</t>
-  </si>
-  <si>
     <t>申请数量</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
   </si>
   <si>
     <t>{.typeName}</t>
-  </si>
-  <si>
-    <t>{.refTask}</t>
   </si>
   <si>
     <t>{.applyQty}</t>
@@ -1110,7 +1104,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
@@ -1119,23 +1113,22 @@
     <col min="4" max="4" width="7.5" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="9.75" customWidth="1"/>
-    <col min="10" max="10" width="14.125" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="8.875" customWidth="1"/>
-    <col min="13" max="13" width="10.875" customWidth="1"/>
-    <col min="14" max="14" width="14.125" customWidth="1"/>
-    <col min="15" max="15" width="13.875" customWidth="1"/>
-    <col min="16" max="16" width="11.375" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="11.125" customWidth="1"/>
+    <col min="11" max="11" width="8.875" customWidth="1"/>
+    <col min="12" max="12" width="10.875" customWidth="1"/>
+    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="13.875" customWidth="1"/>
+    <col min="15" max="15" width="11.375" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:20">
+    <row r="1" ht="14.25" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1193,70 +1186,64 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
@@ -55,10 +55,10 @@
     <t>批准数量</t>
   </si>
   <si>
-    <t>采购申请数量</t>
-  </si>
-  <si>
-    <t>入库数量</t>
+    <t>已采购申请数量</t>
+  </si>
+  <si>
+    <t>已入库数量</t>
   </si>
   <si>
     <t>业务类型</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/pilotApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>单据编号</t>
   </si>
@@ -37,6 +37,9 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>作废状态</t>
+  </si>
+  <si>
     <t>订单状态</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.orderStatusName}</t>
@@ -1104,31 +1110,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="10.625" customWidth="1"/>
-    <col min="8" max="8" width="9.75" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="11.125" customWidth="1"/>
-    <col min="11" max="11" width="8.875" customWidth="1"/>
-    <col min="12" max="12" width="10.875" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="13.875" customWidth="1"/>
-    <col min="15" max="15" width="11.375" customWidth="1"/>
-    <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="15.75" customWidth="1"/>
+    <col min="3" max="4" width="8.875" customWidth="1"/>
+    <col min="5" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="9.75" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="11.125" customWidth="1"/>
+    <col min="12" max="12" width="8.875" customWidth="1"/>
+    <col min="13" max="13" width="10.875" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="11.375" customWidth="1"/>
+    <col min="17" max="17" width="13.5" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="9.625" customWidth="1"/>
+    <col min="20" max="20" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:19">
+    <row r="1" ht="14.25" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1186,64 +1192,70 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
